--- a/Collections/Germany/#Germany#GDR#Regular#[1950-1990]#circulation_quality.xlsx
+++ b/Collections/Germany/#Germany#GDR#Regular#[1950-1990]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Germany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA4EFAF-BB20-4637-B312-52054257446D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C712D7-6010-4EF6-804D-74316322623E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1₰" sheetId="12" r:id="rId1"/>
@@ -41,6 +41,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -2457,7 +2460,7 @@
         <v>17</v>
       </c>
       <c r="G7" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="12">
         <v>0</v>
@@ -3161,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>0</v>
@@ -5934,7 +5937,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>0</v>
@@ -6370,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="G38" s="12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>0</v>
@@ -9067,7 +9070,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F13 F23 F26:F28 F44 F34:F41">
+  <conditionalFormatting sqref="F23 F13 F26:F28 F44 F34:F41">
     <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="formula" val="0"/>
